--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-tiflow-communication.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-tiflow-communication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="363">
   <si>
     <t>Property</t>
   </si>
@@ -480,6 +480,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -649,6 +656,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -662,6 +672,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -703,7 +716,14 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.partOf</t>
@@ -723,6 +743,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -798,6 +821,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -850,6 +876,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1114,7 +1143,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1475,7 +1510,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2686,7 +2721,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>99</v>
@@ -2698,15 +2733,15 @@
         <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2732,13 +2767,13 @@
         <v>141</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2764,13 +2799,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2788,7 +2823,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2797,7 +2832,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
@@ -2809,15 +2844,15 @@
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2843,13 +2878,13 @@
         <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2899,7 +2934,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2925,10 +2960,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2951,16 +2986,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2986,13 +3021,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3010,7 +3045,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3036,14 +3071,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3062,16 +3097,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3121,7 +3156,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3142,19 +3177,19 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3173,16 +3208,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3232,7 +3267,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3253,15 +3288,15 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3290,7 +3325,7 @@
         <v>109</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>111</v>
@@ -3331,19 +3366,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3364,15 +3399,15 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3398,16 +3433,16 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3444,19 +3479,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3477,15 +3512,15 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3508,19 +3543,19 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3569,7 +3604,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3578,27 +3613,27 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3621,15 +3656,17 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3678,7 +3715,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3693,21 +3730,21 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3733,13 +3770,13 @@
         <v>129</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3789,7 +3826,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3804,25 +3841,25 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3841,16 +3878,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3900,7 +3937,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3909,31 +3946,31 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3952,15 +3989,17 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4009,7 +4048,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4018,27 +4057,27 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4061,15 +4100,17 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4118,7 +4159,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4127,10 +4168,10 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
@@ -4139,15 +4180,15 @@
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4170,16 +4211,16 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4187,7 +4228,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>77</v>
@@ -4205,31 +4246,31 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="Z25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>87</v>
@@ -4244,10 +4285,10 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4255,14 +4296,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4281,16 +4322,16 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4316,31 +4357,31 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="Z26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4349,27 +4390,27 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4392,16 +4433,16 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4427,13 +4468,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4451,7 +4492,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4460,7 +4501,7 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
@@ -4469,18 +4510,18 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4503,23 +4544,23 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q28" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>77</v>
@@ -4540,13 +4581,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4564,7 +4605,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4582,7 +4623,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4590,10 +4631,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4616,15 +4657,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4649,13 +4692,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4673,7 +4716,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4682,7 +4725,7 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4694,19 +4737,19 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4725,15 +4768,17 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4782,7 +4827,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4791,27 +4836,27 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4834,16 +4879,16 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4869,13 +4914,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4893,7 +4938,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4902,7 +4947,7 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
@@ -4911,18 +4956,18 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4945,16 +4990,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5004,7 +5049,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5013,27 +5058,27 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5056,16 +5101,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5115,7 +5160,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5124,27 +5169,27 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5167,16 +5212,16 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5226,7 +5271,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5241,10 +5286,10 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5252,10 +5297,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5278,16 +5323,16 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5337,7 +5382,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5352,10 +5397,10 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5363,10 +5408,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5389,16 +5434,16 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5448,7 +5493,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5457,27 +5502,27 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5500,16 +5545,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5559,7 +5604,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5568,27 +5613,27 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5611,16 +5656,16 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5646,13 +5691,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5670,7 +5715,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5679,27 +5724,27 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5722,15 +5767,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5779,7 +5826,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5788,27 +5835,27 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5831,13 +5878,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5888,7 +5935,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5897,7 +5944,7 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -5909,15 +5956,15 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6023,10 +6070,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6096,16 +6143,16 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>115</v>
@@ -6134,14 +6181,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6163,16 +6210,16 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6221,7 +6268,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6242,15 +6289,15 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6273,16 +6320,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6332,7 +6379,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6341,7 +6388,7 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>99</v>
@@ -6353,15 +6400,15 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6384,15 +6431,17 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6441,7 +6490,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6450,19 +6499,19 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
